--- a/src/vlinder/data/beerwiser/xlsx/beerwiser.xlsx
+++ b/src/vlinder/data/beerwiser/xlsx/beerwiser.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tdijk004/Documents/tRBS/open source/trbs/model/data/beerwiser/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tdijk004/Documents/Tooling/tRBS/open source/trbs/src/vlinder/data/beerwiser/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468B641F-C12C-FB44-9437-884644042C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D106804D-795A-6346-BBBE-D6703BC7FDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33600" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="configurations" sheetId="1" r:id="rId1"/>
@@ -581,7 +581,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
